--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND SALTILLO.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND SALTILLO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>266460</t>
+          <t>96727</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63964</t>
+          <t>94486</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>JESUS ROLANDO</t>
+          <t>JENNIFER ANAID</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HARO</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>COX</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,28 +613,32 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6693307571</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>8443445542</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>TEODORO SANCHEZ DAVILA #122</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>21-09-1995</t>
+          <t>14-08-2003</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>ROL.PA@ICLOUD.COM</t>
+          <t>JENNIFERVMTZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>18-11-2024 11:59:56</t>
+          <t>01-06-2022 05:57:28</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -649,22 +653,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 18:43:36</t>
+          <t>03-03-2026 09:49:13</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -681,14 +685,22 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26190522813550005425</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+          <t>26190522835430005487</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>CECILIA ABIGAIL GOMEZ  HANDAL</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -705,12 +717,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>261134</t>
+          <t>266460</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>58638</t>
+          <t>63964</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -720,17 +732,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ADRIANA</t>
+          <t>JESUS ROLANDO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>HARO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>COX</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -740,32 +752,28 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8445028986</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>EL ROSARIO #149</t>
-        </is>
-      </c>
+          <t>6693307571</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>10-11-2005</t>
+          <t>21-09-1995</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>AHDEZZ193@GMAIL.COM</t>
+          <t>ROL.PA@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>08-10-2024 13:54:30</t>
+          <t>18-11-2024 11:59:56</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -775,22 +783,22 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 05:47:20</t>
+          <t>02-03-2026 18:43:36</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -798,21 +806,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>02-03-2026 05:46:48</t>
-        </is>
-      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -820,22 +820,14 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26190522773750005268</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>CECILIA ABIGAIL GOMEZ  HANDAL</t>
-        </is>
-      </c>
+          <t>26190522813550005425</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1138,12 +1130,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347644</t>
+          <t>261134</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89809</t>
+          <t>58638</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1153,17 +1145,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OSCAR ORLANDO</t>
+          <t>ADRIANA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PAREDS</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1173,32 +1165,32 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8661200010</t>
+          <t>8445028986</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOSQUES DE NANTES </t>
+          <t>EL ROSARIO #149</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>28-10-2002</t>
+          <t>10-11-2005</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>ORLI2861@GMAIL.COM</t>
+          <t>AHDEZZ193@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 15:47:56</t>
+          <t>08-10-2024 13:54:30</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1208,22 +1200,22 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 15:54:20</t>
+          <t>02-03-2026 05:47:20</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1233,7 +1225,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>02-03-2026 15:53:20</t>
+          <t>02-03-2026 05:46:48</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1253,14 +1245,22 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26190522799100005371</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
+          <t>26190522773750005268</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>CECILIA ABIGAIL GOMEZ  HANDAL</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1277,12 +1277,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>305341</t>
+          <t>136718</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2840</t>
+          <t>34363</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1292,17 +1292,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>GERARDO RAFAEL</t>
+          <t>LUIS GERARDO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MONARRES</t>
+          <t>GAONA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MASCORRO</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1312,12 +1312,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8441785201</t>
+          <t>8139663068</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>JAZMICAL #130</t>
+          <t>NIGROMANTE 812-4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1327,22 +1327,22 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>03-05-1998</t>
+          <t>08-06-1998</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>GERARDOM849@HOTMAIL.COM</t>
+          <t>GERARDOOTZ28@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>22-07-2025 11:59:19</t>
+          <t>29-11-2022 16:56:55</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1362,17 +1362,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 04:40:39</t>
+          <t>03-03-2026 03:53:50</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>02-03-2026 04:34:20</t>
+          <t>03-03-2026 03:53:17</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1392,14 +1392,10 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26190522772020005265</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26190522821790005457</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1408,24 +1404,24 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Jonathan Pablo Huizar Gutierrez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>332261</t>
+          <t>347644</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>24475</t>
+          <t>89809</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1435,17 +1431,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MARIO</t>
+          <t>OSCAR ORLANDO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MONTALVO</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>PAREDS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1455,12 +1451,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8448583788</t>
+          <t>8661200010</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORTAL DEL SUR </t>
+          <t xml:space="preserve">BOSQUES DE NANTES </t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1470,32 +1466,32 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>16-10-1982</t>
+          <t>28-10-2002</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>MONTYDANY@HOTMAIL.COM</t>
+          <t>ORLI2861@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>05-01-2026 17:34:16</t>
+          <t>02-03-2026 15:47:56</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Tarifas 2026 HE</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1505,17 +1501,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 16:22:41</t>
+          <t>02-03-2026 15:54:20</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>02-03-2026 16:22:03</t>
+          <t>02-03-2026 15:53:20</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1525,7 +1521,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1535,19 +1531,11 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26330522801260003136</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>SERGIO AARON CRUZ RODRIGUEZ</t>
-        </is>
-      </c>
+          <t>26190522799100005371</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
           <t>649</t>
@@ -1567,12 +1555,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347547</t>
+          <t>305341</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89712</t>
+          <t>2840</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1582,17 +1570,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>QUETZALLI RUBI</t>
+          <t>GERARDO RAFAEL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>COSS</t>
+          <t>MONARRES</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUSTAMANTE </t>
+          <t>MASCORRO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1602,28 +1590,32 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8443726302</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>8441785201</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>JAZMICAL #130</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>15-08-1994</t>
+          <t>03-05-1998</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>RUBYBUSTAMANTE188@GMAIL.COM</t>
+          <t>GERARDOM849@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 12:49:34</t>
+          <t>22-07-2025 11:59:19</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1633,22 +1625,22 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 12:51:03</t>
+          <t>02-03-2026 04:40:39</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1656,13 +1648,21 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>02-03-2026 04:34:20</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1670,22 +1670,1666 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26190522792000005337</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
+          <t>26190522772020005265</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Jonathan Pablo Huizar Gutierrez</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>332261</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>24475</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MARIO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>MONTALVO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>GOMEZ</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>8448583788</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PORTAL DEL SUR </t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>16-10-1982</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>MONTYDANY@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>05-01-2026 17:34:16</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:22:41</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:22:03</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>26330522801260003136</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>SERGIO AARON CRUZ RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>347547</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>89712</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>QUETZALLI RUBI</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>COSS</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUSTAMANTE </t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>8443726302</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>15-08-1994</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>RUBYBUSTAMANTE188@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>02-03-2026 12:49:34</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>899</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>02-03-2026 12:51:03</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>26190522792000005337</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>347937</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>90102</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LAURA GABRIELA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>BRIONES</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>8443561653</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ECUADOR 2772</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>01-12-1986</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>G.BRIONES4@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>03-03-2026 06:14:57</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>03-03-2026 06:20:16</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>03-03-2026 06:19:08</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>26190522830220005470</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>347982</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>90147</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>MARIO ALBERTO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>CORTES</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>PADILLA</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>8444599899</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ARTESILLAS #141</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>13-12-1992</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>MACP082704@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:05:14</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:12:23</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:08:44</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>26190522834500005484</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>348102</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>90267</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CHRISTIAN IVETTE</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARTINEZ </t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>MORALES</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>8444935394</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>SALADA 104</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>13-09-1992</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>CHRISTIANCHMTZMORA92@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>03-03-2026 15:58:52</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:03:16</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:02:21</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>26190522845400005540</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>347968</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>90133</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CARLOS PATRICIO</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>BLANCO</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>PADILLA</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>8442206656</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ARGENTINA #151</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>04-10-2005</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>CR1202319@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>03-03-2026 08:34:45</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>03-03-2026 08:38:11</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>03-03-2026 08:37:41</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>26190522833610005478</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>348167</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>90332</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>PAOLA BERENICE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ZERTUCHE</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>BETANCOURT</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>8445501796</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>CORDOVA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>25-02-1995</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>PAOZERTUCHE@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:20:35</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:23:14</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:22:36</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>26190522850540005566</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>348048</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>90213</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>MIGUEL ANGEL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CAMACHO </t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ROMERO </t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>8145044944</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>25-02-1989</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>MILOKEERES@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>03-03-2026 13:32:52</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:31:36</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>03-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>26190522846940005552</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>348099</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>90264</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>DANIEL</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>CASIO</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>FLORENCIO</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>8444378675</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>CALLE 46 552</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>13-12-1989</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>DANYDANIEL121389@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>03-03-2026 15:49:53</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>03-03-2026 15:55:41</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>03-03-2026 15:55:02</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>26190522845160005538</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>348159</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>90324</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>GERARDO</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>FLORES</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>JARAMILLO</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>8442925823</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>CORDOVA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>14-08-1998</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>JERRYFLORES274@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:14:42</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:18:53</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:17:58</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>26190522850180005565</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>348201</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>90366</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>JOSE LINO</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>CASTILLO</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ESTRADA</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>8443402028</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>23-07-2012</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>JOLO22331100@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:56:37</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:57:49</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>26190522852870005576</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>348276</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>90441</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>MIGUEL SAUL</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARTINEZ </t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>DUARTE</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>6141178512</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>RIO NAZAS 532</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>19-08-1987</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>MMSAULDUARTE@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:38:10</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:47:34</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:42:27</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>26190522859850005596</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND SALTILLO.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND SALTILLO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>96727</t>
+          <t>305825</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>94486</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,7 +593,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>JENNIFER ANAID</t>
+          <t>SERGIO ALBERTO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>PEÑA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,71 +613,79 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8443445542</t>
+          <t>8444598722</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>TEODORO SANCHEZ DAVILA #122</t>
+          <t>C. DESCARTES #503</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>14-08-2003</t>
+          <t>04-12-2001</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>JENNIFERVMTZ@GMAIL.COM</t>
+          <t>ALBERTOPEA685@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>01-06-2022 05:57:28</t>
+          <t>24-07-2025 16:39:21</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>03-03-2026 09:49:13</t>
+          <t>05-03-2026 06:19:29</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>03-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr"/>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>05-03-2026 06:18:45</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -685,22 +693,14 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26190522835430005487</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>CECILIA ABIGAIL GOMEZ  HANDAL</t>
-        </is>
-      </c>
+          <t>26190522908260005750</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -717,12 +717,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>266460</t>
+          <t>337553</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>63964</t>
+          <t>15372</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -732,17 +732,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>JESUS ROLANDO</t>
+          <t>ANGEL DE JESUS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HARO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>COX</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -752,10 +752,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6693307571</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>8445320447</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>APACHES #159</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -763,17 +767,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>21-09-1995</t>
+          <t>05-03-2006</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>ROL.PA@ICLOUD.COM</t>
+          <t>ANGELWAR0506@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>18-11-2024 11:59:56</t>
+          <t>25-01-2026 00:52:04</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -783,22 +787,22 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 18:43:36</t>
+          <t>02-03-2026 09:09:10</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -806,13 +810,21 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>02-03-2026 09:08:38</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -820,36 +832,36 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26190522813550005425</t>
+          <t>26190522785250005302</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jonathan Pablo Huizar Gutierrez</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>337553</t>
+          <t>346739</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15372</t>
+          <t>88904</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,17 +871,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ANGEL DE JESUS</t>
+          <t>JOSE LUIS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t xml:space="preserve">RUIZ </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>CARRILLO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -879,12 +891,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8445320447</t>
+          <t>8441318057</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>APACHES #159</t>
+          <t>BOSQUE DE NANTES</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -894,17 +906,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>05-03-2006</t>
+          <t>26-04-1995</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ANGELWAR0506@GMAIL.COM</t>
+          <t>JOSELUIS.IMT95@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>25-01-2026 00:52:04</t>
+          <t>26-02-2026 15:48:32</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -914,22 +926,22 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 09:09:10</t>
+          <t>02-03-2026 15:46:21</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -939,7 +951,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>02-03-2026 09:08:38</t>
+          <t>02-03-2026 15:45:31</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -949,7 +961,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -959,36 +971,44 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26190522785250005302</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+          <t>26190522798660005368</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>ISAAC AARON RIVERA LOPEZ</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Jonathan Pablo Huizar Gutierrez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>346739</t>
+          <t>346799</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>88904</t>
+          <t>88964</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -998,17 +1018,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>JOSE LUIS</t>
+          <t>ELIZABETH</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">RUIZ </t>
+          <t>DAVILA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CARRILLO</t>
+          <t>PEÑA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1018,32 +1038,32 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8441318057</t>
+          <t>8661692399</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>BOSQUE DE NANTES</t>
+          <t>BOLDO 353</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>26-04-1995</t>
+          <t>24-10-2001</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>JOSELUIS.IMT95@GMAIL.COM</t>
+          <t>ELIDP024@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>26-02-2026 15:48:32</t>
+          <t>26-02-2026 18:06:33</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1058,27 +1078,27 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 15:46:21</t>
+          <t>04-03-2026 14:38:31</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>02-03-2026 15:45:31</t>
+          <t>04-03-2026 14:36:59</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1098,7 +1118,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26190522798660005368</t>
+          <t>26190522883400005670</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1113,29 +1133,29 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brizeida Stephania  Herrera Montoya</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>261134</t>
+          <t>305341</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>58638</t>
+          <t>2840</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1145,17 +1165,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ADRIANA</t>
+          <t>GERARDO RAFAEL</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>MONARRES</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>MASCORRO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1165,32 +1185,32 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8445028986</t>
+          <t>8441785201</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>EL ROSARIO #149</t>
+          <t>JAZMICAL #130</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>10-11-2005</t>
+          <t>03-05-1998</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>AHDEZZ193@GMAIL.COM</t>
+          <t>GERARDOM849@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>08-10-2024 13:54:30</t>
+          <t>22-07-2025 11:59:19</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1215,7 +1235,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 05:47:20</t>
+          <t>02-03-2026 04:40:39</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1225,7 +1245,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>02-03-2026 05:46:48</t>
+          <t>02-03-2026 04:34:20</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1245,19 +1265,15 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26190522773750005268</t>
+          <t>26190522772020005265</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>CECILIA ABIGAIL GOMEZ  HANDAL</t>
-        </is>
-      </c>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
           <t>549</t>
@@ -1265,24 +1281,24 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jonathan Pablo Huizar Gutierrez</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>136718</t>
+          <t>332261</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>34363</t>
+          <t>24475</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1292,17 +1308,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LUIS GERARDO</t>
+          <t>MARIO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>GAONA</t>
+          <t>MONTALVO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1312,12 +1328,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8139663068</t>
+          <t>8448583788</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>NIGROMANTE 812-4</t>
+          <t xml:space="preserve">PORTAL DEL SUR </t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1327,22 +1343,22 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>08-06-1998</t>
+          <t>16-10-1982</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>GERARDOOTZ28@GMAIL.COM</t>
+          <t>MONTYDANY@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>29-11-2022 16:56:55</t>
+          <t>05-01-2026 17:34:16</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 HE</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1352,17 +1368,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>03-03-2026 03:53:50</t>
+          <t>02-03-2026 16:22:41</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1372,7 +1388,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>03-03-2026 03:53:17</t>
+          <t>02-03-2026 16:22:03</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1382,7 +1398,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1392,14 +1408,22 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26190522821790005457</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
+          <t>26330522801260003136</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>SERGIO AARON CRUZ RODRIGUEZ</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1416,12 +1440,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347644</t>
+          <t>136718</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89809</t>
+          <t>34363</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1431,17 +1455,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OSCAR ORLANDO</t>
+          <t>LUIS GERARDO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t>GAONA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PAREDS</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1451,12 +1475,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8661200010</t>
+          <t>8139663068</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOSQUES DE NANTES </t>
+          <t>NIGROMANTE 812-4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1466,52 +1490,52 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>28-10-2002</t>
+          <t>08-06-1998</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>ORLI2861@GMAIL.COM</t>
+          <t>GERARDOOTZ28@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 15:47:56</t>
+          <t>29-11-2022 16:56:55</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 15:54:20</t>
+          <t>03-03-2026 03:53:50</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>02-03-2026 15:53:20</t>
+          <t>03-03-2026 03:53:17</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1531,14 +1555,14 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26190522799100005371</t>
+          <t>26190522821790005457</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1555,12 +1579,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>305341</t>
+          <t>347570</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2840</t>
+          <t>89735</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1570,17 +1594,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>GERARDO RAFAEL</t>
+          <t xml:space="preserve">ALONDRA </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MONARRES</t>
+          <t>LIMON</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MASCORRO</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1590,37 +1614,37 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8441785201</t>
+          <t>8444046449</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>JAZMICAL #130</t>
+          <t>VILLAS DEL SENDERO 139</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>03-05-1998</t>
+          <t>27-05-2002</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>GERARDOM849@HOTMAIL.COM</t>
+          <t>ALO_GONZALEZ25@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>22-07-2025 11:59:19</t>
+          <t>02-03-2026 13:34:19</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1630,7 +1654,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1640,17 +1664,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 04:40:39</t>
+          <t>04-03-2026 08:35:19</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>02-03-2026 04:34:20</t>
+          <t>04-03-2026 08:34:30</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1670,15 +1694,19 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26190522772020005265</t>
+          <t>26190522876150005639</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>ISAAC AARON RIVERA LOPEZ</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>549</t>
@@ -1686,24 +1714,24 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Jonathan Pablo Huizar Gutierrez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>332261</t>
+          <t>96727</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>24475</t>
+          <t>94486</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1713,17 +1741,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MARIO</t>
+          <t>JENNIFER ANAID</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MONTALVO</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1733,79 +1761,71 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8448583788</t>
+          <t>8443445542</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORTAL DEL SUR </t>
+          <t>TEODORO SANCHEZ DAVILA #122</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>16-10-1982</t>
+          <t>14-08-2003</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>MONTYDANY@HOTMAIL.COM</t>
+          <t>JENNIFERVMTZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>05-01-2026 17:34:16</t>
+          <t>01-06-2022 05:57:28</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Tarifas 2026 HE</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-03-2026 16:22:41</t>
+          <t>03-03-2026 09:49:13</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>02-03-2026 16:22:03</t>
-        </is>
-      </c>
+          <t>03-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1813,7 +1833,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26330522801260003136</t>
+          <t>26190522835430005487</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1823,12 +1843,12 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>SERGIO AARON CRUZ RODRIGUEZ</t>
+          <t>CECILIA ABIGAIL GOMEZ  HANDAL</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1845,12 +1865,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347547</t>
+          <t>266460</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>89712</t>
+          <t>63964</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1860,17 +1880,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>QUETZALLI RUBI</t>
+          <t>JESUS ROLANDO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>COSS</t>
+          <t>HARO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUSTAMANTE </t>
+          <t>COX</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1880,28 +1900,28 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8443726302</t>
+          <t>6693307571</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>15-08-1994</t>
+          <t>21-09-1995</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>RUBYBUSTAMANTE188@GMAIL.COM</t>
+          <t>ROL.PA@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-03-2026 12:49:34</t>
+          <t>18-11-2024 11:59:56</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1926,7 +1946,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>02-03-2026 12:51:03</t>
+          <t>02-03-2026 18:43:36</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1937,7 +1957,7 @@
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V11" t="inlineStr"/>
@@ -1948,7 +1968,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26190522792000005337</t>
+          <t>26190522813550005425</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1972,12 +1992,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347937</t>
+          <t>346798</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90102</t>
+          <t>88963</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1987,17 +2007,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LAURA GABRIELA</t>
+          <t>KARLA PATRICIA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BRIONES</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2007,12 +2027,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8443561653</t>
+          <t>8661697747</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ECUADOR 2772</t>
+          <t>BOLDO 353</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2022,52 +2042,52 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>01-12-1986</t>
+          <t>14-01-2002</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>G.BRIONES4@HOTMAIL.COM</t>
+          <t>KARLA1401GLZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>03-03-2026 06:14:57</t>
+          <t>26-02-2026 18:02:03</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>03-03-2026 06:20:16</t>
+          <t>04-03-2026 14:27:25</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>03-03-2026 06:19:08</t>
+          <t>04-03-2026 14:25:57</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2077,7 +2097,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -2087,24 +2107,32 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26190522830220005470</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
+          <t>26190522882990005668</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>ISAAC AARON RIVERA LOPEZ</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brizeida Stephania  Herrera Montoya</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -2250,12 +2278,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>348102</t>
+          <t>347587</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>90267</t>
+          <t>89752</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2265,17 +2293,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CHRISTIAN IVETTE</t>
+          <t>CAROLINA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t>GALINDO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2285,12 +2313,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8444935394</t>
+          <t>8662104765</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SALADA 104</t>
+          <t>BOLDO 353</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2300,52 +2328,52 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>13-09-1992</t>
+          <t>21-09-2002</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CHRISTIANCHMTZMORA92@GMAIL.COM</t>
+          <t>CAROLINAGALINDORDZ2@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>03-03-2026 15:58:52</t>
+          <t>02-03-2026 14:22:30</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>03-03-2026 16:03:16</t>
+          <t>04-03-2026 14:32:30</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>03-03-2026 16:02:21</t>
+          <t>04-03-2026 14:31:58</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2365,36 +2393,44 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26190522845400005540</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
+          <t>26190522883210005669</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>ISAAC AARON RIVERA LOPEZ</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brizeida Stephania  Herrera Montoya</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347968</t>
+          <t>347644</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90133</t>
+          <t>89809</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2404,17 +2440,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CARLOS PATRICIO</t>
+          <t>OSCAR ORLANDO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BLANCO</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PADILLA</t>
+          <t>PAREDS</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2424,12 +2460,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8442206656</t>
+          <t>8661200010</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>ARGENTINA #151</t>
+          <t xml:space="preserve">BOSQUES DE NANTES </t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2439,52 +2475,52 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>04-10-2005</t>
+          <t>28-10-2002</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CR1202319@GMAIL.COM</t>
+          <t>ORLI2861@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>03-03-2026 08:34:45</t>
+          <t>02-03-2026 15:47:56</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>03-03-2026 08:38:11</t>
+          <t>02-03-2026 15:54:20</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>03-03-2026 08:37:41</t>
+          <t>02-03-2026 15:53:20</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2504,14 +2540,14 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26190522833610005478</t>
+          <t>26190522799100005371</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2528,12 +2564,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>348167</t>
+          <t>348102</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90332</t>
+          <t>90267</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2543,17 +2579,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PAOLA BERENICE</t>
+          <t>CHRISTIAN IVETTE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ZERTUCHE</t>
+          <t xml:space="preserve">MARTINEZ </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>BETANCOURT</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2563,12 +2599,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8445501796</t>
+          <t>8444935394</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CORDOVA</t>
+          <t>SALADA 104</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2578,17 +2614,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>25-02-1995</t>
+          <t>13-09-1992</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>PAOZERTUCHE@GMAIL.COM</t>
+          <t>CHRISTIANCHMTZMORA92@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>03-03-2026 17:20:35</t>
+          <t>03-03-2026 15:58:52</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2613,7 +2649,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>03-03-2026 17:23:14</t>
+          <t>03-03-2026 16:03:16</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2623,7 +2659,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>03-03-2026 17:22:36</t>
+          <t>03-03-2026 16:02:21</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2643,7 +2679,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26190522850540005566</t>
+          <t>26190522845400005540</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
@@ -2655,24 +2691,24 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jonathan Pablo Huizar Gutierrez</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>348048</t>
+          <t>348321</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>90213</t>
+          <t>90486</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2682,17 +2718,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL</t>
+          <t>LOUIS</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMACHO </t>
+          <t>ESCANDON</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROMERO </t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2702,7 +2738,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8145044944</t>
+          <t>8445384652</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2713,17 +2749,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>25-02-1989</t>
+          <t>12-03-2009</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>MILOKEERES@GMAIL.COM</t>
+          <t>LOUISANCASTILLO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>03-03-2026 13:32:52</t>
+          <t>04-03-2026 06:39:29</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2748,12 +2784,12 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>03-03-2026 16:31:36</t>
+          <t>05-03-2026 13:44:31</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>03-06-2026 23:59:59</t>
+          <t>05-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -2770,7 +2806,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26190522846940005552</t>
+          <t>26190522916030005791</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
@@ -2794,12 +2830,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>348099</t>
+          <t>347968</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>90264</t>
+          <t>90133</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2809,17 +2845,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DANIEL</t>
+          <t>CARLOS PATRICIO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CASIO</t>
+          <t>BLANCO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FLORENCIO</t>
+          <t>PADILLA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2829,12 +2865,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8444378675</t>
+          <t>8442206656</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CALLE 46 552</t>
+          <t>ARGENTINA #151</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2844,17 +2880,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>13-12-1989</t>
+          <t>04-10-2005</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>DANYDANIEL121389@GMAIL.COM</t>
+          <t>CR1202319@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>03-03-2026 15:49:53</t>
+          <t>03-03-2026 08:34:45</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2879,7 +2915,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>03-03-2026 15:55:41</t>
+          <t>03-03-2026 08:38:11</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2889,7 +2925,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>03-03-2026 15:55:02</t>
+          <t>03-03-2026 08:37:41</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2909,7 +2945,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26190522845160005538</t>
+          <t>26190522833610005478</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
@@ -2933,12 +2969,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>348159</t>
+          <t>348167</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>90324</t>
+          <t>90332</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2948,17 +2984,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>GERARDO</t>
+          <t>PAOLA BERENICE</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>ZERTUCHE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JARAMILLO</t>
+          <t>BETANCOURT</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2968,7 +3004,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8442925823</t>
+          <t>8445501796</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2978,22 +3014,22 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>14-08-1998</t>
+          <t>25-02-1995</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>JERRYFLORES274@GMAIL.COM</t>
+          <t>PAOZERTUCHE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>03-03-2026 17:14:42</t>
+          <t>03-03-2026 17:20:35</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3018,7 +3054,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>03-03-2026 17:18:53</t>
+          <t>03-03-2026 17:23:14</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -3028,7 +3064,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>03-03-2026 17:17:58</t>
+          <t>03-03-2026 17:22:36</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3048,7 +3084,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26190522850180005565</t>
+          <t>26190522850540005566</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
@@ -3060,24 +3096,24 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brizeida Stephania  Herrera Montoya</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>348201</t>
+          <t>261134</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>90366</t>
+          <t>58638</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3087,17 +3123,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>JOSE LINO</t>
+          <t>ADRIANA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ESTRADA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3107,10 +3143,14 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8443402028</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>8445028986</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>EL ROSARIO #149</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3118,32 +3158,32 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>23-07-2012</t>
+          <t>10-11-2005</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>JOLO22331100@GMAIL.COM</t>
+          <t>AHDEZZ193@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>03-03-2026 17:56:37</t>
+          <t>08-10-2024 13:54:30</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -3153,21 +3193,29 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>03-03-2026 17:57:49</t>
+          <t>02-03-2026 05:47:20</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>02-03-2026 05:46:48</t>
+        </is>
+      </c>
       <c r="U20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W20" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3175,11 +3223,19 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26190522852870005576</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
+          <t>26190522773750005268</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>CECILIA ABIGAIL GOMEZ  HANDAL</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>549</t>
@@ -3199,12 +3255,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>348276</t>
+          <t>348048</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>90441</t>
+          <t>90213</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3214,17 +3270,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MIGUEL SAUL</t>
+          <t>MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t xml:space="preserve">CAMACHO </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>DUARTE</t>
+          <t xml:space="preserve">ROMERO </t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3234,14 +3290,10 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6141178512</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>RIO NAZAS 532</t>
-        </is>
-      </c>
+          <t>8145044944</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3249,17 +3301,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>19-08-1987</t>
+          <t>25-02-1989</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>MMSAULDUARTE@GMAIL.COM</t>
+          <t>MILOKEERES@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>03-03-2026 19:38:10</t>
+          <t>03-03-2026 13:32:52</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3269,44 +3321,36 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>03-03-2026 19:47:34</t>
+          <t>03-03-2026 16:31:36</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>03-03-2026 19:42:27</t>
-        </is>
-      </c>
+          <t>03-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3314,24 +3358,1116 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26190522859850005596</t>
+          <t>26190522846940005552</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>348099</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>90264</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>DANIEL</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>CASIO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>FLORENCIO</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>8444378675</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>CALLE 46 552</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>13-12-1989</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>DANYDANIEL121389@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>03-03-2026 15:49:53</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>03-03-2026 15:55:41</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>03-03-2026 15:55:02</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>26190522845160005538</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>348159</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>90324</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>GERARDO</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>FLORES</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>JARAMILLO</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>8442925823</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>CORDOVA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>14-08-1998</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>JERRYFLORES274@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:14:42</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:18:53</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:17:58</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>26190522850180005565</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>Brizeida Stephania  Herrera Montoya</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>348201</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>90366</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>JOSE LINO</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>CASTILLO</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ESTRADA</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>8443402028</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>23-07-2012</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>JOLO22331100@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:56:37</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:57:49</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>26190522852870005576</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>347547</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>89712</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>QUETZALLI RUBI</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>COSS</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUSTAMANTE </t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>8443726302</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>15-08-1994</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>RUBYBUSTAMANTE188@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>02-03-2026 12:49:34</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>02-03-2026 12:51:03</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>26190522792000005337</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>348608</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>90773</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CINTHIA ABIGAIL</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGUIRRE </t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>TELLEZ</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>8442949637</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ESTEBAN VACA</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>21-11-2005</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>ABIGAILAGUIRRE2711@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>05-03-2026 03:24:33</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>05-03-2026 03:29:29</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>05-03-2026 03:28:19</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>26190522900840005740</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>Rocio Berenice Davalos Gallegos</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>348276</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>90441</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>MIGUEL SAUL</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARTINEZ </t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>DUARTE</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>6141178512</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>RIO NAZAS 532</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>19-08-1987</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>MMSAULDUARTE@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:38:10</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
           <t>649</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:47:34</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:42:27</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>26190522859850005596</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>348792</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>90957</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LIZETH</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>DAVILA</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>SIFUENTES</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>8447761081</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>NOPAL 1829</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>17-02-2001</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>LIZETHDAVILA577@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>05-03-2026 18:20:21</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>05-03-2026 18:34:18</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>05-03-2026 18:33:13</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>26190522927590005822</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>347937</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>90102</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LAURA GABRIELA</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>BRIONES</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>8443561653</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ECUADOR 2772</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>01-12-1986</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>G.BRIONES4@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>03-03-2026 06:14:57</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>03-03-2026 06:20:16</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>03-03-2026 06:19:08</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>26190522830220005470</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>Jonathan Pablo Huizar Gutierrez</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>con rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND SALTILLO.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND SALTILLO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC29"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>305825</t>
+          <t>261134</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>58638</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SERGIO ALBERTO</t>
+          <t>ADRIANA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PEÑA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,37 +613,37 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8444598722</t>
+          <t>8445028986</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>C. DESCARTES #503</t>
+          <t>EL ROSARIO #149</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>04-12-2001</t>
+          <t>10-11-2005</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>ALBERTOPEA685@GMAIL.COM</t>
+          <t>AHDEZZ193@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>24-07-2025 16:39:21</t>
+          <t>08-10-2024 13:54:30</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -663,17 +663,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>05-03-2026 06:19:29</t>
+          <t>02-03-2026 05:47:20</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>05-03-2026 06:18:45</t>
+          <t>02-03-2026 05:46:48</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -693,11 +693,19 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26190522908260005750</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+          <t>26190522773750005268</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>CECILIA ABIGAIL GOMEZ  HANDAL</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>549</t>
@@ -717,12 +725,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>337553</t>
+          <t>335451</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15372</t>
+          <t>24676</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -732,17 +740,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ANGEL DE JESUS</t>
+          <t xml:space="preserve">ALAN </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>BASURTO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -752,12 +760,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8445320447</t>
+          <t>8441013501</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>APACHES #159</t>
+          <t>GAVILANES 140</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -767,22 +775,22 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>05-03-2006</t>
+          <t>23-02-2001</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>ANGELWAR0506@GMAIL.COM</t>
+          <t>BASURTO2315@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>25-01-2026 00:52:04</t>
+          <t>16-01-2026 18:40:21</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -792,7 +800,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -802,17 +810,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 09:09:10</t>
+          <t>06-03-2026 19:41:30</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>02-03-2026 09:08:38</t>
+          <t>06-03-2026 19:40:34</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -822,7 +830,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -832,11 +840,19 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26190522785250005302</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
+          <t>26190522960820005934</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>YESICA BERENICE PECINA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>549</t>
@@ -844,24 +860,24 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Jonathan Pablo Huizar Gutierrez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>346739</t>
+          <t>134964</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>88904</t>
+          <t>32612</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -871,17 +887,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>JOSE LUIS</t>
+          <t>RONALD  SALVADOR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RUIZ </t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CARRILLO</t>
+          <t>LUNA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -891,12 +907,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8441318057</t>
+          <t>7352068550</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>BOSQUE DE NANTES</t>
+          <t>CERRO DE TEOTEPEC #165</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -906,52 +922,52 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>26-04-1995</t>
+          <t>28-02-1993</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>JOSELUIS.IMT95@GMAIL.COM</t>
+          <t>RON28551@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>26-02-2026 15:48:32</t>
+          <t>15-11-2022 18:11:35</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 15:46:21</t>
+          <t>08-03-2026 09:06:41</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>07-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>02-03-2026 15:45:31</t>
+          <t>08-03-2026 09:06:06</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -961,7 +977,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -971,22 +987,14 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26190522798660005368</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>ISAAC AARON RIVERA LOPEZ</t>
-        </is>
-      </c>
+          <t>26190522982790005980</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1003,12 +1011,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>346799</t>
+          <t>136718</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>88964</t>
+          <t>34363</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1018,17 +1026,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ELIZABETH</t>
+          <t>LUIS GERARDO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>DAVILA</t>
+          <t>GAONA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PEÑA</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1038,67 +1046,67 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8661692399</t>
+          <t>8139663068</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>BOLDO 353</t>
+          <t>NIGROMANTE 812-4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>24-10-2001</t>
+          <t>08-06-1998</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>ELIDP024@GMAIL.COM</t>
+          <t>GERARDOOTZ28@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>26-02-2026 18:06:33</t>
+          <t>29-11-2022 16:56:55</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>04-03-2026 14:38:31</t>
+          <t>03-03-2026 03:53:50</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>04-03-2026 14:36:59</t>
+          <t>03-03-2026 03:53:17</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1118,44 +1126,36 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26190522883400005670</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>ISAAC AARON RIVERA LOPEZ</t>
-        </is>
-      </c>
+          <t>26190522821790005457</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Brizeida Stephania  Herrera Montoya</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>305341</t>
+          <t>257686</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2840</t>
+          <t>55190</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>GERARDO RAFAEL</t>
+          <t>MELISSA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MONARRES</t>
+          <t>AGUIRRE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MASCORRO</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1185,32 +1185,28 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8441785201</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>JAZMICAL #130</t>
-        </is>
-      </c>
+          <t>8443279942</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>03-05-1998</t>
+          <t>01-12-1995</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>GERARDOM849@HOTMAIL.COM</t>
+          <t>PAGMARA95@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>22-07-2025 11:59:19</t>
+          <t>17-09-2024 19:17:59</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1220,44 +1216,36 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 04:40:39</t>
+          <t>06-03-2026 17:05:12</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>02-03-2026 04:34:20</t>
-        </is>
-      </c>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1265,40 +1253,36 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26190522772020005265</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26190522955480005918</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Jonathan Pablo Huizar Gutierrez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>332261</t>
+          <t>285748</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>24475</t>
+          <t>83248</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1308,17 +1292,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MARIO</t>
+          <t>KATHERINE XIMENA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MONTALVO</t>
+          <t xml:space="preserve">CONTRERAS </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1328,37 +1312,37 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8448583788</t>
+          <t>8448440989</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORTAL DEL SUR </t>
+          <t>CAÑON DEL TUNAL 643</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>16-10-1982</t>
+          <t>09-01-2003</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>MONTYDANY@HOTMAIL.COM</t>
+          <t>KATHERINECONTRERAS74@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>05-01-2026 17:34:16</t>
+          <t>31-03-2025 17:32:25</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Tarifas 2026 HE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1368,27 +1352,27 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 16:22:41</t>
+          <t>06-03-2026 19:07:24</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>02-03-2026 16:22:03</t>
+          <t>06-03-2026 19:06:08</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1398,7 +1382,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1408,22 +1392,14 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26330522801260003136</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>SERGIO AARON CRUZ RODRIGUEZ</t>
-        </is>
-      </c>
+          <t>26190522959890005931</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1440,12 +1416,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>136718</t>
+          <t>96727</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>34363</t>
+          <t>94486</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1455,17 +1431,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LUIS GERARDO</t>
+          <t>JENNIFER ANAID</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>GAONA</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1475,79 +1451,71 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8139663068</t>
+          <t>8443445542</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>NIGROMANTE 812-4</t>
+          <t>TEODORO SANCHEZ DAVILA #122</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>08-06-1998</t>
+          <t>14-08-2003</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>GERARDOOTZ28@GMAIL.COM</t>
+          <t>JENNIFERVMTZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>29-11-2022 16:56:55</t>
+          <t>01-06-2022 05:57:28</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>03-03-2026 03:53:50</t>
+          <t>03-03-2026 09:49:13</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>03-03-2026 03:53:17</t>
-        </is>
-      </c>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1555,14 +1523,22 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26190522821790005457</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
+          <t>26190522835430005487</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>CECILIA ABIGAIL GOMEZ  HANDAL</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1579,12 +1555,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347570</t>
+          <t>266460</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89735</t>
+          <t>63964</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1594,17 +1570,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALONDRA </t>
+          <t>JESUS ROLANDO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LIMON</t>
+          <t>HARO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>COX</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1614,79 +1590,67 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8444046449</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>VILLAS DEL SENDERO 139</t>
-        </is>
-      </c>
+          <t>6693307571</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>27-05-2002</t>
+          <t>21-09-1995</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>ALO_GONZALEZ25@ICLOUD.COM</t>
+          <t>ROL.PA@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 13:34:19</t>
+          <t>18-11-2024 11:59:56</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>04-03-2026 08:35:19</t>
+          <t>02-03-2026 18:43:36</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>04-03-2026 08:34:30</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1694,22 +1658,14 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26190522876150005639</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>ISAAC AARON RIVERA LOPEZ</t>
-        </is>
-      </c>
+          <t>26190522813550005425</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1726,12 +1682,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>96727</t>
+          <t>305341</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>94486</t>
+          <t>2840</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1741,17 +1697,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>JENNIFER ANAID</t>
+          <t>GERARDO RAFAEL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>MONARRES</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>MASCORRO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1761,32 +1717,32 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8443445542</t>
+          <t>8441785201</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>TEODORO SANCHEZ DAVILA #122</t>
+          <t>JAZMICAL #130</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>14-08-2003</t>
+          <t>03-05-1998</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>JENNIFERVMTZ@GMAIL.COM</t>
+          <t>GERARDOM849@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>01-06-2022 05:57:28</t>
+          <t>22-07-2025 11:59:19</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1796,36 +1752,44 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>03-03-2026 09:49:13</t>
+          <t>02-03-2026 04:40:39</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>03-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>02-03-2026 04:34:20</t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1833,44 +1797,40 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26190522835430005487</t>
+          <t>26190522772020005265</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>CECILIA ABIGAIL GOMEZ  HANDAL</t>
-        </is>
-      </c>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jonathan Pablo Huizar Gutierrez</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>266460</t>
+          <t>332261</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>63964</t>
+          <t>24475</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1880,17 +1840,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>JESUS ROLANDO</t>
+          <t>MARIO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HARO</t>
+          <t>MONTALVO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>COX</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1900,10 +1860,14 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6693307571</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>8448583788</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PORTAL DEL SUR </t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1911,42 +1875,42 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>21-09-1995</t>
+          <t>16-10-1982</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>ROL.PA@ICLOUD.COM</t>
+          <t>MONTYDANY@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>18-11-2024 11:59:56</t>
+          <t>05-01-2026 17:34:16</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Tarifas 2026 HE</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>02-03-2026 18:43:36</t>
+          <t>02-03-2026 16:22:41</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1954,13 +1918,21 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:22:03</t>
+        </is>
+      </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1968,14 +1940,22 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26190522813550005425</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
+          <t>26330522801260003136</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>SERGIO AARON CRUZ RODRIGUEZ</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1992,12 +1972,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>346798</t>
+          <t>305825</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>88963</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2007,17 +1987,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>KARLA PATRICIA</t>
+          <t>SERGIO ALBERTO</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>PEÑA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2027,57 +2007,57 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8661697747</t>
+          <t>8444598722</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BOLDO 353</t>
+          <t>C. DESCARTES #503</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>14-01-2002</t>
+          <t>04-12-2001</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>KARLA1401GLZ@GMAIL.COM</t>
+          <t>ALBERTOPEA685@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>26-02-2026 18:02:03</t>
+          <t>24-07-2025 16:39:21</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>04-03-2026 14:27:25</t>
+          <t>05-03-2026 06:19:29</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2087,7 +2067,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>04-03-2026 14:25:57</t>
+          <t>05-03-2026 06:18:45</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2097,7 +2077,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -2107,44 +2087,36 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26190522882990005668</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>ISAAC AARON RIVERA LOPEZ</t>
-        </is>
-      </c>
+          <t>26190522908260005750</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Brizeida Stephania  Herrera Montoya</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347982</t>
+          <t>347587</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>90147</t>
+          <t>89752</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2154,17 +2126,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MARIO ALBERTO</t>
+          <t>CAROLINA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CORTES</t>
+          <t>GALINDO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PADILLA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2174,57 +2146,57 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8444599899</t>
+          <t>8662104765</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ARTESILLAS #141</t>
+          <t>BOLDO 353</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>13-12-1992</t>
+          <t>21-09-2002</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>MACP082704@GMAIL.COM</t>
+          <t>CAROLINAGALINDORDZ2@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>03-03-2026 09:05:14</t>
+          <t>02-03-2026 14:22:30</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>03-03-2026 09:12:23</t>
+          <t>04-03-2026 14:32:30</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -2234,7 +2206,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>03-03-2026 09:08:44</t>
+          <t>04-03-2026 14:31:58</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2254,36 +2226,44 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26190522834500005484</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
+          <t>26190522883210005669</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>ISAAC AARON RIVERA LOPEZ</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brizeida Stephania  Herrera Montoya</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347587</t>
+          <t>346798</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>89752</t>
+          <t>88963</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2293,17 +2273,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CAROLINA</t>
+          <t>KARLA PATRICIA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>GALINDO</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2313,7 +2293,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8662104765</t>
+          <t>8661697747</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2328,17 +2308,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>21-09-2002</t>
+          <t>14-01-2002</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CAROLINAGALINDORDZ2@GMAIL.COM</t>
+          <t>KARLA1401GLZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-03-2026 14:22:30</t>
+          <t>26-02-2026 18:02:03</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2363,17 +2343,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>04-03-2026 14:32:30</t>
+          <t>04-03-2026 14:27:25</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>04-03-2026 14:31:58</t>
+          <t>04-03-2026 14:25:57</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2383,7 +2363,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2393,7 +2373,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26190522883210005669</t>
+          <t>26190522882990005668</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2425,12 +2405,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347644</t>
+          <t>337553</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>89809</t>
+          <t>15372</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2440,17 +2420,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>OSCAR ORLANDO</t>
+          <t>ANGEL DE JESUS</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PAREDS</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2460,12 +2440,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8661200010</t>
+          <t>8445320447</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOSQUES DE NANTES </t>
+          <t>APACHES #159</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2475,17 +2455,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>28-10-2002</t>
+          <t>05-03-2006</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ORLI2861@GMAIL.COM</t>
+          <t>ANGELWAR0506@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-03-2026 15:47:56</t>
+          <t>25-01-2026 00:52:04</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2495,32 +2475,32 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>02-03-2026 15:54:20</t>
+          <t>02-03-2026 09:09:10</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>02-03-2026 15:53:20</t>
+          <t>02-03-2026 09:08:38</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2530,7 +2510,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2540,36 +2520,36 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26190522799100005371</t>
+          <t>26190522785250005302</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jonathan Pablo Huizar Gutierrez</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>348102</t>
+          <t>346739</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90267</t>
+          <t>88904</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2579,17 +2559,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CHRISTIAN IVETTE</t>
+          <t>JOSE LUIS</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t xml:space="preserve">RUIZ </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>CARRILLO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2599,67 +2579,67 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8444935394</t>
+          <t>8441318057</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SALADA 104</t>
+          <t>BOSQUE DE NANTES</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>13-09-1992</t>
+          <t>26-04-1995</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CHRISTIANCHMTZMORA92@GMAIL.COM</t>
+          <t>JOSELUIS.IMT95@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>03-03-2026 15:58:52</t>
+          <t>26-02-2026 15:48:32</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>03-03-2026 16:03:16</t>
+          <t>02-03-2026 15:46:21</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>03-03-2026 16:02:21</t>
+          <t>02-03-2026 15:45:31</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2679,36 +2659,44 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26190522845400005540</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
+          <t>26190522798660005368</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>ISAAC AARON RIVERA LOPEZ</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Jonathan Pablo Huizar Gutierrez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>348321</t>
+          <t>346799</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>90486</t>
+          <t>88964</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2718,17 +2706,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LOUIS</t>
+          <t>ELIZABETH</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ESCANDON</t>
+          <t>DAVILA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>PEÑA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2738,28 +2726,32 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8445384652</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>8661692399</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>BOLDO 353</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>12-03-2009</t>
+          <t>24-10-2001</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>LOUISANCASTILLO@GMAIL.COM</t>
+          <t>ELIDP024@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>04-03-2026 06:39:29</t>
+          <t>26-02-2026 18:06:33</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2769,36 +2761,44 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>05-03-2026 13:44:31</t>
+          <t>04-03-2026 14:38:31</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>05-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>04-03-2026 14:36:59</t>
+        </is>
+      </c>
       <c r="U17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2806,36 +2806,44 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26190522916030005791</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
+          <t>26190522883400005670</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>ISAAC AARON RIVERA LOPEZ</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brizeida Stephania  Herrera Montoya</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>347968</t>
+          <t>347547</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>90133</t>
+          <t>89712</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2845,17 +2853,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CARLOS PATRICIO</t>
+          <t>QUETZALLI RUBI</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BLANCO</t>
+          <t>COSS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PADILLA</t>
+          <t xml:space="preserve">BUSTAMANTE </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2865,79 +2873,67 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8442206656</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>ARGENTINA #151</t>
-        </is>
-      </c>
+          <t>8443726302</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>04-10-2005</t>
+          <t>15-08-1994</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CR1202319@GMAIL.COM</t>
+          <t>RUBYBUSTAMANTE188@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>03-03-2026 08:34:45</t>
+          <t>02-03-2026 12:49:34</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>03-03-2026 08:38:11</t>
+          <t>02-03-2026 12:51:03</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>03-03-2026 08:37:41</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2945,14 +2941,14 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26190522833610005478</t>
+          <t>26190522792000005337</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2969,12 +2965,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>348167</t>
+          <t>347644</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>90332</t>
+          <t>89809</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2984,17 +2980,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>PAOLA BERENICE</t>
+          <t>OSCAR ORLANDO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ZERTUCHE</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>BETANCOURT</t>
+          <t>PAREDS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -3004,67 +3000,67 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8445501796</t>
+          <t>8661200010</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>CORDOVA</t>
+          <t xml:space="preserve">BOSQUES DE NANTES </t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>25-02-1995</t>
+          <t>28-10-2002</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>PAOZERTUCHE@GMAIL.COM</t>
+          <t>ORLI2861@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>03-03-2026 17:20:35</t>
+          <t>02-03-2026 15:47:56</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>03-03-2026 17:23:14</t>
+          <t>02-03-2026 15:54:20</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>03-03-2026 17:22:36</t>
+          <t>02-03-2026 15:53:20</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3084,36 +3080,36 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26190522850540005566</t>
+          <t>26190522799100005371</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Brizeida Stephania  Herrera Montoya</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>261134</t>
+          <t>347570</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>58638</t>
+          <t>89735</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3123,17 +3119,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ADRIANA</t>
+          <t xml:space="preserve">ALONDRA </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>LIMON</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3143,12 +3139,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8445028986</t>
+          <t>8444046449</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>EL ROSARIO #149</t>
+          <t>VILLAS DEL SENDERO 139</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3158,22 +3154,22 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>10-11-2005</t>
+          <t>27-05-2002</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>AHDEZZ193@GMAIL.COM</t>
+          <t>ALO_GONZALEZ25@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>08-10-2024 13:54:30</t>
+          <t>02-03-2026 13:34:19</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -3183,7 +3179,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -3193,17 +3189,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>02-03-2026 05:47:20</t>
+          <t>04-03-2026 08:35:19</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>02-03-2026 05:46:48</t>
+          <t>04-03-2026 08:34:30</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3223,7 +3219,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26190522773750005268</t>
+          <t>26190522876150005639</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -3233,7 +3229,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>CECILIA ABIGAIL GOMEZ  HANDAL</t>
+          <t>ISAAC AARON RIVERA LOPEZ</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3255,12 +3251,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>348048</t>
+          <t>347937</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>90213</t>
+          <t>90102</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3270,17 +3266,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL</t>
+          <t>LAURA GABRIELA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMACHO </t>
+          <t>BRIONES</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROMERO </t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3290,67 +3286,79 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>8145044944</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>8443561653</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ECUADOR 2772</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>25-02-1989</t>
+          <t>01-12-1986</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>MILOKEERES@GMAIL.COM</t>
+          <t>G.BRIONES4@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>03-03-2026 13:32:52</t>
+          <t>03-03-2026 06:14:57</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>03-03-2026 16:31:36</t>
+          <t>03-03-2026 06:20:16</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>03-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>03-03-2026 06:19:08</t>
+        </is>
+      </c>
       <c r="U21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3358,36 +3366,36 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26190522846940005552</t>
+          <t>26190522830220005470</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jonathan Pablo Huizar Gutierrez</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>348099</t>
+          <t>348048</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>90264</t>
+          <t>90213</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3397,17 +3405,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DANIEL</t>
+          <t>MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CASIO</t>
+          <t xml:space="preserve">CAMACHO </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FLORENCIO</t>
+          <t xml:space="preserve">ROMERO </t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3417,14 +3425,10 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>8444378675</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>CALLE 46 552</t>
-        </is>
-      </c>
+          <t>8145044944</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3432,64 +3436,56 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>13-12-1989</t>
+          <t>25-02-1989</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>DANYDANIEL121389@GMAIL.COM</t>
+          <t>MILOKEERES@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>03-03-2026 15:49:53</t>
+          <t>03-03-2026 13:32:52</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>03-03-2026 15:55:41</t>
+          <t>03-03-2026 16:31:36</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>03-03-2026 15:55:02</t>
-        </is>
-      </c>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3497,14 +3493,14 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26190522845160005538</t>
+          <t>26190522846940005552</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3521,12 +3517,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>348159</t>
+          <t>348099</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>90324</t>
+          <t>90264</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3536,17 +3532,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>GERARDO</t>
+          <t>DANIEL</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>CASIO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>JARAMILLO</t>
+          <t>FLORENCIO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3556,12 +3552,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>8442925823</t>
+          <t>8444378675</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CORDOVA</t>
+          <t>CALLE 46 552</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3571,17 +3567,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>14-08-1998</t>
+          <t>13-12-1989</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>JERRYFLORES274@GMAIL.COM</t>
+          <t>DANYDANIEL121389@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>03-03-2026 17:14:42</t>
+          <t>03-03-2026 15:49:53</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3606,17 +3602,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>03-03-2026 17:18:53</t>
+          <t>03-03-2026 15:55:41</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>03-03-2026 17:17:58</t>
+          <t>03-03-2026 15:55:02</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3636,7 +3632,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26190522850180005565</t>
+          <t>26190522845160005538</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
@@ -3648,24 +3644,24 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Brizeida Stephania  Herrera Montoya</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>348201</t>
+          <t>347968</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>90366</t>
+          <t>90133</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3675,17 +3671,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>JOSE LINO</t>
+          <t>CARLOS PATRICIO</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>BLANCO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ESTRADA</t>
+          <t>PADILLA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3695,43 +3691,47 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>8443402028</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>8442206656</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ARGENTINA #151</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>23-07-2012</t>
+          <t>04-10-2005</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>JOLO22331100@GMAIL.COM</t>
+          <t>CR1202319@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>03-03-2026 17:56:37</t>
+          <t>03-03-2026 08:34:45</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -3741,21 +3741,29 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>03-03-2026 17:57:49</t>
+          <t>03-03-2026 08:38:11</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>03-03-2026 08:37:41</t>
+        </is>
+      </c>
       <c r="U24" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr"/>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W24" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3763,7 +3771,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26190522852870005576</t>
+          <t>26190522833610005478</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
@@ -3787,12 +3795,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>347547</t>
+          <t>348159</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>89712</t>
+          <t>90324</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3802,17 +3810,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>QUETZALLI RUBI</t>
+          <t>GERARDO</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>COSS</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUSTAMANTE </t>
+          <t>JARAMILLO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3822,53 +3830,57 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>8443726302</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>8442925823</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>CORDOVA</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>15-08-1994</t>
+          <t>14-08-1998</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>RUBYBUSTAMANTE188@GMAIL.COM</t>
+          <t>JERRYFLORES274@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>02-03-2026 12:49:34</t>
+          <t>03-03-2026 17:14:42</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>02-03-2026 12:51:03</t>
+          <t>03-03-2026 17:18:53</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3876,13 +3888,21 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:17:58</t>
+        </is>
+      </c>
       <c r="U25" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr"/>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W25" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3890,36 +3910,36 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26190522792000005337</t>
+          <t>26190522850180005565</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brizeida Stephania  Herrera Montoya</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>348608</t>
+          <t>348201</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>90773</t>
+          <t>90366</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3929,17 +3949,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CINTHIA ABIGAIL</t>
+          <t>JOSE LINO</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGUIRRE </t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>TELLEZ</t>
+          <t>ESTRADA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3949,14 +3969,10 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>8442949637</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>ESTEBAN VACA</t>
-        </is>
-      </c>
+          <t>8443402028</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3964,32 +3980,32 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>21-11-2005</t>
+          <t>23-07-2012</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>ABIGAILAGUIRRE2711@HOTMAIL.COM</t>
+          <t>JOLO22331100@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>05-03-2026 03:24:33</t>
+          <t>03-03-2026 17:56:37</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -3999,29 +4015,21 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>05-03-2026 03:29:29</t>
+          <t>03-03-2026 17:57:49</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>05-03-2026 03:28:19</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4029,7 +4037,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26190522900840005740</t>
+          <t>26190522852870005576</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
@@ -4041,12 +4049,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Rocio Berenice Davalos Gallegos</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4151,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
@@ -4192,12 +4200,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>348792</t>
+          <t>348355</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>90957</t>
+          <t>90520</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4207,17 +4215,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LIZETH</t>
+          <t>JESSICA ESMERALDA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>DAVILA</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SIFUENTES</t>
+          <t>JUAREZ</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4227,12 +4235,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>8447761081</t>
+          <t>8448432149</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>NOPAL 1829</t>
+          <t>PROVIDENCIA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4242,17 +4250,17 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>17-02-2001</t>
+          <t>01-01-1991</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>LIZETHDAVILA577@GMAIL.COM</t>
+          <t>JESSICAMEZ91@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>05-03-2026 18:20:21</t>
+          <t>04-03-2026 08:45:20</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4277,17 +4285,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>05-03-2026 18:34:18</t>
+          <t>07-03-2026 08:06:07</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>06-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>05-03-2026 18:33:13</t>
+          <t>07-03-2026 08:05:26</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4307,12 +4315,12 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26190522927590005822</t>
+          <t>26190522969810005953</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr"/>
@@ -4335,12 +4343,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>347937</t>
+          <t>348167</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>90102</t>
+          <t>90332</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4350,17 +4358,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LAURA GABRIELA</t>
+          <t>PAOLA BERENICE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>BRIONES</t>
+          <t>ZERTUCHE</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>BETANCOURT</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4370,12 +4378,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>8443561653</t>
+          <t>8445501796</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>ECUADOR 2772</t>
+          <t>CORDOVA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4385,17 +4393,17 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>01-12-1986</t>
+          <t>25-02-1995</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>G.BRIONES4@HOTMAIL.COM</t>
+          <t>PAOZERTUCHE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>03-03-2026 06:14:57</t>
+          <t>03-03-2026 17:20:35</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4420,17 +4428,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>03-03-2026 06:20:16</t>
+          <t>03-03-2026 17:23:14</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>03-03-2026 06:19:08</t>
+          <t>03-03-2026 17:22:36</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4450,7 +4458,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26190522830220005470</t>
+          <t>26190522850540005566</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
@@ -4462,12 +4470,965 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
+          <t>Brizeida Stephania  Herrera Montoya</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>348608</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>90773</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CINTHIA ABIGAIL</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGUIRRE </t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>TELLEZ</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>8442949637</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ESTEBAN VACA</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>21-11-2005</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>ABIGAILAGUIRRE2711@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>05-03-2026 03:24:33</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>05-03-2026 03:29:29</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>05-03-2026 03:28:19</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>26190522900840005740</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>Rocio Berenice Davalos Gallegos</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>348792</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>90957</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LIZETH</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>DAVILA</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>SIFUENTES</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>8447761081</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>NOPAL 1829</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>17-02-2001</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>LIZETHDAVILA577@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>05-03-2026 18:20:21</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>05-03-2026 18:34:18</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>05-03-2026 18:33:13</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>26190522927590005822</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>Brizeida Stephania  Herrera Montoya</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>348921</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>91086</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ARELY</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>VILLALPANDO</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>AGUSTINCE</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>8443475491</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>30-06-1999</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>ARELYVILLAPANDO71@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>06-03-2026 14:39:54</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>06-03-2026 14:41:17</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>26190522951140005894</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
           <t>Jonathan Pablo Huizar Gutierrez</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>347982</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>90147</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>MARIO ALBERTO</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>CORTES</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>PADILLA</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>8444599899</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ARTESILLAS #141</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>13-12-1992</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>MACP082704@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:05:14</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:12:23</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:08:44</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>26190522834500005484</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>349033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>91198</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>BRENDA ELIZABETH</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ROJAS</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>SANTANA</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>8116149893</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>CAÑON DEL TUNAL 643</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>09-01-1994</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>CHEVOELI31@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>06-03-2026 19:11:05</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>06-03-2026 19:15:52</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>06-03-2026 19:15:08</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>26190522960110005932</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>348102</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>90267</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CHRISTIAN IVETTE</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARTINEZ </t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>MORALES</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>8444935394</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>SALADA 104</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>13-09-1992</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>CHRISTIANCHMTZMORA92@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>03-03-2026 15:58:52</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:03:16</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:02:21</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>26190522845400005540</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>Jonathan Pablo Huizar Gutierrez</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>348321</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>90486</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LOUIS</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>ESCANDON</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>CASTILLO</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>8445384652</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>12-03-2009</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>LOUISANCASTILLO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>04-03-2026 06:39:29</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>05-03-2026 13:44:31</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>26190522916030005791</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
